--- a/content.xlsx
+++ b/content.xlsx
@@ -651,7 +651,8 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Answer the questions below to estimate where your AI system sits under [Regulation (EU) 2024/1689](regulation_pdf) — the EU AI Act.</t>
+          <t>Answer the questions below to estimate where your AI system sits under [Regulation (EU) 2024/1689](regulation_pdf) — the EU AI Act.
+As amended by [Regulation (EU) 2026/1744](omnibus_oj) — the Digital Omnibus on AI.</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
